--- a/reports/滨江一号_2026-06-21_交接包/整改反馈/滨江一号_2026-06-21_整改跟踪报告.xlsx
+++ b/reports/滨江一号_2026-06-21_交接包/整改反馈/滨江一号_2026-06-21_整改跟踪报告.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-21 05:26:51</t>
+          <t>2026-06-21 05:41:18</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n"/>
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" s="4" t="n"/>
       <c r="D10" s="4" t="n"/>
@@ -1093,9 +1093,9 @@
           <t>PIL-7946069F</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>未反馈</t>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>待复核</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1138,10 +1138,22 @@
       </c>
       <c r="K7" s="8" t="inlineStr"/>
       <c r="L7" s="8" t="inlineStr"/>
-      <c r="M7" s="8" t="inlineStr"/>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
       <c r="N7" s="8" t="inlineStr"/>
-      <c r="O7" s="8" t="inlineStr"/>
-      <c r="P7" s="8" t="inlineStr"/>
+      <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>赵班长</t>
+        </is>
+      </c>
+      <c r="P7" s="8" t="inlineStr">
+        <is>
+          <t>./现场照片/ZK空桩号.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1149,9 +1161,9 @@
           <t>POU-ACD22BDE</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>未反馈</t>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>待复核</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -1196,8 +1208,16 @@
       <c r="L8" s="8" t="inlineStr"/>
       <c r="M8" s="8" t="inlineStr"/>
       <c r="N8" s="8" t="inlineStr"/>
-      <c r="O8" s="8" t="inlineStr"/>
-      <c r="P8" s="8" t="inlineStr"/>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>李工</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>./日志记录/ZK5灌注超时.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
